--- a/training.xlsx
+++ b/training.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Pat\Documents\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ahmed\Desktop\giza-academy-portal\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="245" uniqueCount="146">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="326" uniqueCount="149">
   <si>
     <t>احمد ابراهيم فؤاد محمد</t>
   </si>
@@ -465,6 +465,15 @@
   </si>
   <si>
     <t>ملاحظات الفرع</t>
+  </si>
+  <si>
+    <t>اجتاز الاعتماد بنجاح</t>
+  </si>
+  <si>
+    <t>حالة الاعتماد</t>
+  </si>
+  <si>
+    <t>لم يجتاز</t>
   </si>
 </sst>
 </file>
@@ -475,7 +484,7 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="Arial"/>
       <family val="2"/>
       <charset val="178"/>
       <scheme val="minor"/>
@@ -490,7 +499,7 @@
       <u/>
       <sz val="11"/>
       <color theme="10"/>
-      <name val="Calibri"/>
+      <name val="Arial"/>
       <family val="2"/>
       <charset val="178"/>
       <scheme val="minor"/>
@@ -510,7 +519,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -533,12 +542,23 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="12" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -550,22 +570,13 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="3">
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="2">
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -862,17 +873,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E81"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:F81"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="19.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="19.625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="29" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="34.5703125" customWidth="1"/>
+    <col min="3" max="3" width="34.625" customWidth="1"/>
     <col min="4" max="4" width="11" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="25.85546875" customWidth="1"/>
+    <col min="5" max="5" width="25.875" customWidth="1"/>
+    <col min="6" max="6" width="13.125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>141</v>
       </c>
@@ -888,8 +900,11 @@
       <c r="E1" s="1" t="s">
         <v>145</v>
       </c>
-    </row>
-    <row r="2" spans="1:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F1" s="5" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="2">
         <v>28012162100231</v>
       </c>
@@ -905,8 +920,11 @@
       <c r="E2" s="3" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="3" spans="1:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F2" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="2">
         <v>28704152800994</v>
       </c>
@@ -922,8 +940,11 @@
       <c r="E3" s="3" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="4" spans="1:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F3" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="2">
         <v>27801232102653</v>
       </c>
@@ -939,8 +960,11 @@
       <c r="E4" s="3" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="5" spans="1:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F4" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="2">
         <v>27901251300126</v>
       </c>
@@ -956,8 +980,11 @@
       <c r="E5" s="3" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="6" spans="1:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F5" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="2">
         <v>28011072100244</v>
       </c>
@@ -973,8 +1000,11 @@
       <c r="E6" s="3" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="7" spans="1:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F6" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="2">
         <v>27405132200507</v>
       </c>
@@ -990,8 +1020,11 @@
       <c r="E7" s="3" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="8" spans="1:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F7" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="2">
         <v>27306201201849</v>
       </c>
@@ -1007,8 +1040,11 @@
       <c r="E8" s="3" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="9" spans="1:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F8" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="2">
         <v>27609042102926</v>
       </c>
@@ -1024,8 +1060,11 @@
       <c r="E9" s="3" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="10" spans="1:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F9" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="2">
         <v>28211272102348</v>
       </c>
@@ -1041,8 +1080,11 @@
       <c r="E10" s="3" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="11" spans="1:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F10" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="2">
         <v>29110252101968</v>
       </c>
@@ -1058,8 +1100,11 @@
       <c r="E11" s="3" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="12" spans="1:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F11" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="2">
         <v>27508090104981</v>
       </c>
@@ -1075,8 +1120,11 @@
       <c r="E12" s="3" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="13" spans="1:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F12" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="2">
         <v>27704272300045</v>
       </c>
@@ -1092,8 +1140,11 @@
       <c r="E13" s="3" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="14" spans="1:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F13" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="2">
         <v>27909182101559</v>
       </c>
@@ -1109,8 +1160,11 @@
       <c r="E14" s="3" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="15" spans="1:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F14" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="2">
         <v>28904212100562</v>
       </c>
@@ -1126,8 +1180,11 @@
       <c r="E15" s="3" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="16" spans="1:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F15" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="2">
         <v>27908052101216</v>
       </c>
@@ -1143,8 +1200,11 @@
       <c r="E16" s="3" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="17" spans="1:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F16" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="2">
         <v>28509191202223</v>
       </c>
@@ -1160,8 +1220,11 @@
       <c r="E17" s="3" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="18" spans="1:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F17" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="2">
         <v>27508032102765</v>
       </c>
@@ -1177,8 +1240,11 @@
       <c r="E18" s="3" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="19" spans="1:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F18" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="2">
         <v>27703162101229</v>
       </c>
@@ -1194,8 +1260,11 @@
       <c r="E19" s="3" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="20" spans="1:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F19" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="2">
         <v>28308052104106</v>
       </c>
@@ -1211,8 +1280,11 @@
       <c r="E20" s="3" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="21" spans="1:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F20" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="2">
         <v>29112232101107</v>
       </c>
@@ -1228,8 +1300,11 @@
       <c r="E21" s="3" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="22" spans="1:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F21" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="2">
         <v>28309072101304</v>
       </c>
@@ -1245,8 +1320,11 @@
       <c r="E22" s="3" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="23" spans="1:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F22" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="2">
         <v>27708242101744</v>
       </c>
@@ -1262,8 +1340,11 @@
       <c r="E23" s="3" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="24" spans="1:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F23" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="2">
         <v>28310182100174</v>
       </c>
@@ -1279,8 +1360,11 @@
       <c r="E24" s="3" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="25" spans="1:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F24" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="2">
         <v>27911062100375</v>
       </c>
@@ -1296,8 +1380,11 @@
       <c r="E25" s="3" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="26" spans="1:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F25" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="2">
         <v>26807292102274</v>
       </c>
@@ -1313,8 +1400,11 @@
       <c r="E26" s="3" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="27" spans="1:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F26" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="2">
         <v>28804182101157</v>
       </c>
@@ -1330,8 +1420,11 @@
       <c r="E27" s="3" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="28" spans="1:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F27" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="2">
         <v>27912172103465</v>
       </c>
@@ -1347,8 +1440,11 @@
       <c r="E28" s="3" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="29" spans="1:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F28" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="2">
         <v>27111192100249</v>
       </c>
@@ -1364,8 +1460,11 @@
       <c r="E29" s="3" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="30" spans="1:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F29" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="2">
         <v>27307120200887</v>
       </c>
@@ -1381,8 +1480,11 @@
       <c r="E30" s="3" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="31" spans="1:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F30" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="2">
         <v>27906013300128</v>
       </c>
@@ -1398,8 +1500,11 @@
       <c r="E31" s="3" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="32" spans="1:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F31" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="2">
         <v>28009121402729</v>
       </c>
@@ -1415,8 +1520,11 @@
       <c r="E32" s="3" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="33" spans="1:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F32" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="2">
         <v>27608060101183</v>
       </c>
@@ -1432,8 +1540,11 @@
       <c r="E33" s="3" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="34" spans="1:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F33" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="2">
         <v>28409091604427</v>
       </c>
@@ -1449,8 +1560,11 @@
       <c r="E34" s="3" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="35" spans="1:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F34" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="2">
         <v>28104041301681</v>
       </c>
@@ -1466,8 +1580,11 @@
       <c r="E35" s="3" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="36" spans="1:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F35" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="2">
         <v>28009182100784</v>
       </c>
@@ -1483,8 +1600,11 @@
       <c r="E36" s="3" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="37" spans="1:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F36" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="2">
         <v>28907260102461</v>
       </c>
@@ -1500,8 +1620,11 @@
       <c r="E37" s="3" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="38" spans="1:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F37" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="2">
         <v>28208242100439</v>
       </c>
@@ -1517,8 +1640,11 @@
       <c r="E38" s="3" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="39" spans="1:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F38" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="2">
         <v>26802161200589</v>
       </c>
@@ -1534,8 +1660,11 @@
       <c r="E39" s="3" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="40" spans="1:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F39" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="2">
         <v>28507312100269</v>
       </c>
@@ -1551,8 +1680,11 @@
       <c r="E40" s="3" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="41" spans="1:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F40" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="2">
         <v>29202268800485</v>
       </c>
@@ -1568,8 +1700,11 @@
       <c r="E41" s="3" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="42" spans="1:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F41" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42" s="2">
         <v>28601070100826</v>
       </c>
@@ -1585,8 +1720,11 @@
       <c r="E42" s="3" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="43" spans="1:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F42" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="2">
         <v>28309270102065</v>
       </c>
@@ -1602,8 +1740,11 @@
       <c r="E43" s="3" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="44" spans="1:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F43" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" s="2">
         <v>28410012115082</v>
       </c>
@@ -1619,8 +1760,11 @@
       <c r="E44" s="3" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="45" spans="1:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F44" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" s="2">
         <v>27101092102427</v>
       </c>
@@ -1636,8 +1780,11 @@
       <c r="E45" s="3" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="46" spans="1:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F45" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A46" s="2">
         <v>27103182100345</v>
       </c>
@@ -1653,8 +1800,11 @@
       <c r="E46" s="3" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="47" spans="1:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F46" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A47" s="2">
         <v>27309140103007</v>
       </c>
@@ -1670,8 +1820,11 @@
       <c r="E47" s="3" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="48" spans="1:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F47" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A48" s="2">
         <v>27201012102167</v>
       </c>
@@ -1687,8 +1840,11 @@
       <c r="E48" s="3" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="49" spans="1:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F48" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A49" s="2">
         <v>27809152103846</v>
       </c>
@@ -1704,8 +1860,11 @@
       <c r="E49" s="3" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="50" spans="1:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F49" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A50" s="2">
         <v>27405130100777</v>
       </c>
@@ -1721,8 +1880,11 @@
       <c r="E50" s="3" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="51" spans="1:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F50" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A51" s="2">
         <v>28206122402188</v>
       </c>
@@ -1738,8 +1900,11 @@
       <c r="E51" s="3" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="52" spans="1:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F51" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A52" s="2">
         <v>27712122104313</v>
       </c>
@@ -1755,8 +1920,11 @@
       <c r="E52" s="3" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="53" spans="1:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F52" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A53" s="2">
         <v>28804052101538</v>
       </c>
@@ -1772,8 +1940,11 @@
       <c r="E53" s="3" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="54" spans="1:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F53" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A54" s="2">
         <v>28907242103123</v>
       </c>
@@ -1789,8 +1960,11 @@
       <c r="E54" s="3" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="55" spans="1:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F54" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A55" s="2">
         <v>28511222100526</v>
       </c>
@@ -1806,8 +1980,11 @@
       <c r="E55" s="3" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="56" spans="1:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F55" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A56" s="2">
         <v>27805212101265</v>
       </c>
@@ -1823,8 +2000,11 @@
       <c r="E56" s="3" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="57" spans="1:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F56" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A57" s="2">
         <v>27211092101749</v>
       </c>
@@ -1840,8 +2020,11 @@
       <c r="E57" s="3" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="58" spans="1:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F57" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A58" s="2">
         <v>28801282102356</v>
       </c>
@@ -1857,8 +2040,11 @@
       <c r="E58" s="3" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="59" spans="1:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F58" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="59" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A59" s="2">
         <v>28002222100796</v>
       </c>
@@ -1874,8 +2060,11 @@
       <c r="E59" s="3" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="60" spans="1:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F59" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="60" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A60" s="2">
         <v>27603121201109</v>
       </c>
@@ -1891,8 +2080,11 @@
       <c r="E60" s="3" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="61" spans="1:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F60" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="61" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A61" s="2">
         <v>28707172101366</v>
       </c>
@@ -1908,8 +2100,11 @@
       <c r="E61" s="3" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="62" spans="1:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F61" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="62" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A62" s="2">
         <v>28305300100105</v>
       </c>
@@ -1925,8 +2120,11 @@
       <c r="E62" s="3" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="63" spans="1:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F62" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="63" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A63" s="2">
         <v>27404172100231</v>
       </c>
@@ -1942,8 +2140,11 @@
       <c r="E63" s="3" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="64" spans="1:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F63" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="64" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A64" s="2">
         <v>27511162401501</v>
       </c>
@@ -1959,8 +2160,11 @@
       <c r="E64" s="3" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="65" spans="1:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F64" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="65" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A65" s="2">
         <v>27205312101508</v>
       </c>
@@ -1976,8 +2180,11 @@
       <c r="E65" s="3" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="66" spans="1:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F65" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="66" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A66" s="2">
         <v>28801101406065</v>
       </c>
@@ -1993,8 +2200,11 @@
       <c r="E66" s="3" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="67" spans="1:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F66" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="67" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A67" s="2">
         <v>26910230100165</v>
       </c>
@@ -2010,8 +2220,11 @@
       <c r="E67" s="3" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="68" spans="1:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F67" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="68" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A68" s="2">
         <v>27608011603181</v>
       </c>
@@ -2027,8 +2240,11 @@
       <c r="E68" s="3" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="69" spans="1:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F68" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="69" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A69" s="2">
         <v>29012212100142</v>
       </c>
@@ -2044,8 +2260,11 @@
       <c r="E69" s="3" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="70" spans="1:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F69" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="70" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A70" s="2">
         <v>27701061202641</v>
       </c>
@@ -2061,8 +2280,11 @@
       <c r="E70" s="3" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="71" spans="1:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F70" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="71" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A71" s="2">
         <v>28811262103386</v>
       </c>
@@ -2078,8 +2300,11 @@
       <c r="E71" s="3" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="72" spans="1:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F71" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="72" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A72" s="2">
         <v>28812282100789</v>
       </c>
@@ -2095,8 +2320,11 @@
       <c r="E72" s="3" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="73" spans="1:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F72" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="73" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A73" s="2">
         <v>27802280102009</v>
       </c>
@@ -2112,8 +2340,11 @@
       <c r="E73" s="3" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="74" spans="1:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F73" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="74" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A74" s="2">
         <v>28203150201105</v>
       </c>
@@ -2129,8 +2360,11 @@
       <c r="E74" s="3" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="75" spans="1:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F74" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="75" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A75" s="2">
         <v>27512242500965</v>
       </c>
@@ -2146,8 +2380,11 @@
       <c r="E75" s="3" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="76" spans="1:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F75" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="76" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A76" s="2">
         <v>27803050103487</v>
       </c>
@@ -2163,8 +2400,11 @@
       <c r="E76" s="3" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="77" spans="1:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F76" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="77" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A77" s="2">
         <v>28208043100047</v>
       </c>
@@ -2180,8 +2420,11 @@
       <c r="E77" s="3" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="78" spans="1:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F77" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="78" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A78" s="2">
         <v>28304241700806</v>
       </c>
@@ -2197,8 +2440,11 @@
       <c r="E78" s="3" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="79" spans="1:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F78" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="79" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A79" s="2">
         <v>29203120200345</v>
       </c>
@@ -2214,8 +2460,11 @@
       <c r="E79" s="3" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="80" spans="1:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F79" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="80" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A80" s="2">
         <v>28506050100169</v>
       </c>
@@ -2231,8 +2480,11 @@
       <c r="E80" s="3" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="81" spans="1:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F80" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="81" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A81" s="2">
         <v>27707090102042</v>
       </c>
@@ -2247,6 +2499,9 @@
       </c>
       <c r="E81" s="3" t="s">
         <v>2</v>
+      </c>
+      <c r="F81" t="s">
+        <v>146</v>
       </c>
     </row>
   </sheetData>

--- a/training.xlsx
+++ b/training.xlsx
@@ -15,7 +15,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$2:$A$82</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$F$1:$F$81</definedName>
   </definedNames>
   <calcPr calcId="162913"/>
   <extLst>
@@ -480,7 +480,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -502,6 +502,14 @@
       <name val="Arial"/>
       <family val="2"/>
       <charset val="178"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -550,7 +558,9 @@
         <color indexed="64"/>
       </right>
       <top/>
-      <bottom/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
       <diagonal/>
     </border>
   </borders>
@@ -558,7 +568,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="12" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -570,7 +580,17 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="12" fontId="1" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -884,43 +904,43 @@
     <col min="6" max="6" width="13.125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:6" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="8" t="s">
         <v>141</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="8" t="s">
         <v>142</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="8" t="s">
         <v>143</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="8" t="s">
         <v>144</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="8" t="s">
         <v>145</v>
       </c>
-      <c r="F1" s="5" t="s">
+      <c r="F1" s="9" t="s">
         <v>147</v>
       </c>
     </row>
     <row r="2" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="2">
+      <c r="A2" s="5">
         <v>28012162100231</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="C2" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="D2" s="4">
+      <c r="D2" s="7">
         <v>1271979290</v>
       </c>
-      <c r="E2" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="F2" t="s">
+      <c r="E2" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="F2" s="1" t="s">
         <v>148</v>
       </c>
     </row>
@@ -940,7 +960,7 @@
       <c r="E3" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="F3" t="s">
+      <c r="F3" s="1" t="s">
         <v>146</v>
       </c>
     </row>
@@ -960,7 +980,7 @@
       <c r="E4" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="F4" t="s">
+      <c r="F4" s="1" t="s">
         <v>146</v>
       </c>
     </row>
@@ -980,7 +1000,7 @@
       <c r="E5" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="F5" t="s">
+      <c r="F5" s="1" t="s">
         <v>146</v>
       </c>
     </row>
@@ -1000,7 +1020,7 @@
       <c r="E6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="F6" t="s">
+      <c r="F6" s="1" t="s">
         <v>146</v>
       </c>
     </row>
@@ -1020,7 +1040,7 @@
       <c r="E7" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="F7" t="s">
+      <c r="F7" s="1" t="s">
         <v>146</v>
       </c>
     </row>
@@ -1040,7 +1060,7 @@
       <c r="E8" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="F8" t="s">
+      <c r="F8" s="1" t="s">
         <v>146</v>
       </c>
     </row>
@@ -1060,7 +1080,7 @@
       <c r="E9" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="F9" t="s">
+      <c r="F9" s="1" t="s">
         <v>146</v>
       </c>
     </row>
@@ -1080,7 +1100,7 @@
       <c r="E10" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="F10" t="s">
+      <c r="F10" s="1" t="s">
         <v>146</v>
       </c>
     </row>
@@ -1100,7 +1120,7 @@
       <c r="E11" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="F11" t="s">
+      <c r="F11" s="1" t="s">
         <v>146</v>
       </c>
     </row>
@@ -1120,7 +1140,7 @@
       <c r="E12" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="F12" t="s">
+      <c r="F12" s="1" t="s">
         <v>146</v>
       </c>
     </row>
@@ -1140,7 +1160,7 @@
       <c r="E13" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="F13" t="s">
+      <c r="F13" s="1" t="s">
         <v>146</v>
       </c>
     </row>
@@ -1160,7 +1180,7 @@
       <c r="E14" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="F14" t="s">
+      <c r="F14" s="1" t="s">
         <v>146</v>
       </c>
     </row>
@@ -1180,7 +1200,7 @@
       <c r="E15" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="F15" t="s">
+      <c r="F15" s="1" t="s">
         <v>146</v>
       </c>
     </row>
@@ -1200,7 +1220,7 @@
       <c r="E16" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="F16" t="s">
+      <c r="F16" s="1" t="s">
         <v>146</v>
       </c>
     </row>
@@ -1220,7 +1240,7 @@
       <c r="E17" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="F17" t="s">
+      <c r="F17" s="1" t="s">
         <v>146</v>
       </c>
     </row>
@@ -1240,7 +1260,7 @@
       <c r="E18" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="F18" t="s">
+      <c r="F18" s="1" t="s">
         <v>146</v>
       </c>
     </row>
@@ -1260,7 +1280,7 @@
       <c r="E19" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="F19" t="s">
+      <c r="F19" s="1" t="s">
         <v>146</v>
       </c>
     </row>
@@ -1280,7 +1300,7 @@
       <c r="E20" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="F20" t="s">
+      <c r="F20" s="1" t="s">
         <v>146</v>
       </c>
     </row>
@@ -1300,7 +1320,7 @@
       <c r="E21" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="F21" t="s">
+      <c r="F21" s="1" t="s">
         <v>146</v>
       </c>
     </row>
@@ -1320,7 +1340,7 @@
       <c r="E22" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="F22" t="s">
+      <c r="F22" s="1" t="s">
         <v>146</v>
       </c>
     </row>
@@ -1340,7 +1360,7 @@
       <c r="E23" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="F23" t="s">
+      <c r="F23" s="1" t="s">
         <v>146</v>
       </c>
     </row>
@@ -1360,7 +1380,7 @@
       <c r="E24" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="F24" t="s">
+      <c r="F24" s="1" t="s">
         <v>146</v>
       </c>
     </row>
@@ -1380,7 +1400,7 @@
       <c r="E25" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="F25" t="s">
+      <c r="F25" s="1" t="s">
         <v>146</v>
       </c>
     </row>
@@ -1400,7 +1420,7 @@
       <c r="E26" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="F26" t="s">
+      <c r="F26" s="1" t="s">
         <v>146</v>
       </c>
     </row>
@@ -1420,7 +1440,7 @@
       <c r="E27" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="F27" t="s">
+      <c r="F27" s="1" t="s">
         <v>146</v>
       </c>
     </row>
@@ -1440,7 +1460,7 @@
       <c r="E28" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="F28" t="s">
+      <c r="F28" s="1" t="s">
         <v>146</v>
       </c>
     </row>
@@ -1460,7 +1480,7 @@
       <c r="E29" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="F29" t="s">
+      <c r="F29" s="1" t="s">
         <v>146</v>
       </c>
     </row>
@@ -1480,7 +1500,7 @@
       <c r="E30" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="F30" t="s">
+      <c r="F30" s="1" t="s">
         <v>146</v>
       </c>
     </row>
@@ -1500,7 +1520,7 @@
       <c r="E31" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="F31" t="s">
+      <c r="F31" s="1" t="s">
         <v>146</v>
       </c>
     </row>
@@ -1520,7 +1540,7 @@
       <c r="E32" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="F32" t="s">
+      <c r="F32" s="1" t="s">
         <v>146</v>
       </c>
     </row>
@@ -1540,7 +1560,7 @@
       <c r="E33" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="F33" t="s">
+      <c r="F33" s="1" t="s">
         <v>146</v>
       </c>
     </row>
@@ -1560,7 +1580,7 @@
       <c r="E34" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="F34" t="s">
+      <c r="F34" s="1" t="s">
         <v>146</v>
       </c>
     </row>
@@ -1580,7 +1600,7 @@
       <c r="E35" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="F35" t="s">
+      <c r="F35" s="1" t="s">
         <v>146</v>
       </c>
     </row>
@@ -1600,7 +1620,7 @@
       <c r="E36" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="F36" t="s">
+      <c r="F36" s="1" t="s">
         <v>146</v>
       </c>
     </row>
@@ -1620,7 +1640,7 @@
       <c r="E37" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="F37" t="s">
+      <c r="F37" s="1" t="s">
         <v>146</v>
       </c>
     </row>
@@ -1640,7 +1660,7 @@
       <c r="E38" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="F38" t="s">
+      <c r="F38" s="1" t="s">
         <v>146</v>
       </c>
     </row>
@@ -1660,7 +1680,7 @@
       <c r="E39" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="F39" t="s">
+      <c r="F39" s="1" t="s">
         <v>146</v>
       </c>
     </row>
@@ -1680,7 +1700,7 @@
       <c r="E40" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="F40" t="s">
+      <c r="F40" s="1" t="s">
         <v>146</v>
       </c>
     </row>
@@ -1700,7 +1720,7 @@
       <c r="E41" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="F41" t="s">
+      <c r="F41" s="1" t="s">
         <v>146</v>
       </c>
     </row>
@@ -1720,7 +1740,7 @@
       <c r="E42" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="F42" t="s">
+      <c r="F42" s="1" t="s">
         <v>146</v>
       </c>
     </row>
@@ -1740,7 +1760,7 @@
       <c r="E43" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="F43" t="s">
+      <c r="F43" s="1" t="s">
         <v>146</v>
       </c>
     </row>
@@ -1760,7 +1780,7 @@
       <c r="E44" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="F44" t="s">
+      <c r="F44" s="1" t="s">
         <v>146</v>
       </c>
     </row>
@@ -1780,7 +1800,7 @@
       <c r="E45" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="F45" t="s">
+      <c r="F45" s="1" t="s">
         <v>146</v>
       </c>
     </row>
@@ -1800,7 +1820,7 @@
       <c r="E46" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="F46" t="s">
+      <c r="F46" s="1" t="s">
         <v>146</v>
       </c>
     </row>
@@ -1820,7 +1840,7 @@
       <c r="E47" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="F47" t="s">
+      <c r="F47" s="1" t="s">
         <v>146</v>
       </c>
     </row>
@@ -1840,7 +1860,7 @@
       <c r="E48" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="F48" t="s">
+      <c r="F48" s="1" t="s">
         <v>146</v>
       </c>
     </row>
@@ -1860,7 +1880,7 @@
       <c r="E49" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="F49" t="s">
+      <c r="F49" s="1" t="s">
         <v>146</v>
       </c>
     </row>
@@ -1880,7 +1900,7 @@
       <c r="E50" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="F50" t="s">
+      <c r="F50" s="1" t="s">
         <v>146</v>
       </c>
     </row>
@@ -1900,7 +1920,7 @@
       <c r="E51" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="F51" t="s">
+      <c r="F51" s="1" t="s">
         <v>146</v>
       </c>
     </row>
@@ -1920,7 +1940,7 @@
       <c r="E52" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="F52" t="s">
+      <c r="F52" s="1" t="s">
         <v>148</v>
       </c>
     </row>
@@ -1940,7 +1960,7 @@
       <c r="E53" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="F53" t="s">
+      <c r="F53" s="1" t="s">
         <v>146</v>
       </c>
     </row>
@@ -1960,7 +1980,7 @@
       <c r="E54" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="F54" t="s">
+      <c r="F54" s="1" t="s">
         <v>146</v>
       </c>
     </row>
@@ -1980,7 +2000,7 @@
       <c r="E55" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="F55" t="s">
+      <c r="F55" s="1" t="s">
         <v>146</v>
       </c>
     </row>
@@ -2000,7 +2020,7 @@
       <c r="E56" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="F56" t="s">
+      <c r="F56" s="1" t="s">
         <v>146</v>
       </c>
     </row>
@@ -2020,7 +2040,7 @@
       <c r="E57" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="F57" t="s">
+      <c r="F57" s="1" t="s">
         <v>146</v>
       </c>
     </row>
@@ -2040,7 +2060,7 @@
       <c r="E58" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="F58" t="s">
+      <c r="F58" s="1" t="s">
         <v>146</v>
       </c>
     </row>
@@ -2060,7 +2080,7 @@
       <c r="E59" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="F59" t="s">
+      <c r="F59" s="1" t="s">
         <v>146</v>
       </c>
     </row>
@@ -2080,7 +2100,7 @@
       <c r="E60" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="F60" t="s">
+      <c r="F60" s="1" t="s">
         <v>146</v>
       </c>
     </row>
@@ -2100,7 +2120,7 @@
       <c r="E61" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="F61" t="s">
+      <c r="F61" s="1" t="s">
         <v>146</v>
       </c>
     </row>
@@ -2120,7 +2140,7 @@
       <c r="E62" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="F62" t="s">
+      <c r="F62" s="1" t="s">
         <v>146</v>
       </c>
     </row>
@@ -2140,7 +2160,7 @@
       <c r="E63" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="F63" t="s">
+      <c r="F63" s="1" t="s">
         <v>146</v>
       </c>
     </row>
@@ -2160,7 +2180,7 @@
       <c r="E64" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="F64" t="s">
+      <c r="F64" s="1" t="s">
         <v>146</v>
       </c>
     </row>
@@ -2180,7 +2200,7 @@
       <c r="E65" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="F65" t="s">
+      <c r="F65" s="1" t="s">
         <v>146</v>
       </c>
     </row>
@@ -2200,7 +2220,7 @@
       <c r="E66" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="F66" t="s">
+      <c r="F66" s="1" t="s">
         <v>146</v>
       </c>
     </row>
@@ -2220,7 +2240,7 @@
       <c r="E67" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="F67" t="s">
+      <c r="F67" s="1" t="s">
         <v>146</v>
       </c>
     </row>
@@ -2240,7 +2260,7 @@
       <c r="E68" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="F68" t="s">
+      <c r="F68" s="1" t="s">
         <v>146</v>
       </c>
     </row>
@@ -2260,7 +2280,7 @@
       <c r="E69" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="F69" t="s">
+      <c r="F69" s="1" t="s">
         <v>146</v>
       </c>
     </row>
@@ -2280,7 +2300,7 @@
       <c r="E70" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="F70" t="s">
+      <c r="F70" s="1" t="s">
         <v>146</v>
       </c>
     </row>
@@ -2300,7 +2320,7 @@
       <c r="E71" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="F71" t="s">
+      <c r="F71" s="1" t="s">
         <v>146</v>
       </c>
     </row>
@@ -2320,7 +2340,7 @@
       <c r="E72" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="F72" t="s">
+      <c r="F72" s="1" t="s">
         <v>146</v>
       </c>
     </row>
@@ -2340,7 +2360,7 @@
       <c r="E73" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="F73" t="s">
+      <c r="F73" s="1" t="s">
         <v>146</v>
       </c>
     </row>
@@ -2360,7 +2380,7 @@
       <c r="E74" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="F74" t="s">
+      <c r="F74" s="1" t="s">
         <v>146</v>
       </c>
     </row>
@@ -2380,7 +2400,7 @@
       <c r="E75" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="F75" t="s">
+      <c r="F75" s="1" t="s">
         <v>146</v>
       </c>
     </row>
@@ -2400,7 +2420,7 @@
       <c r="E76" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="F76" t="s">
+      <c r="F76" s="1" t="s">
         <v>146</v>
       </c>
     </row>
@@ -2420,7 +2440,7 @@
       <c r="E77" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="F77" t="s">
+      <c r="F77" s="1" t="s">
         <v>146</v>
       </c>
     </row>
@@ -2440,7 +2460,7 @@
       <c r="E78" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="F78" t="s">
+      <c r="F78" s="1" t="s">
         <v>146</v>
       </c>
     </row>
@@ -2460,7 +2480,7 @@
       <c r="E79" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="F79" t="s">
+      <c r="F79" s="1" t="s">
         <v>146</v>
       </c>
     </row>
@@ -2480,7 +2500,7 @@
       <c r="E80" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="F80" t="s">
+      <c r="F80" s="1" t="s">
         <v>146</v>
       </c>
     </row>
@@ -2500,7 +2520,7 @@
       <c r="E81" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="F81" t="s">
+      <c r="F81" s="1" t="s">
         <v>146</v>
       </c>
     </row>
@@ -2597,5 +2617,6 @@
     <hyperlink ref="D81" r:id="rId80" tooltip="إرسال رسالة عبر واتساب" display="javascript:void(0);"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId81"/>
 </worksheet>
 </file>